--- a/ツール/DCF2PCV.xlsx
+++ b/ツール/DCF2PCV.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://perspectivecojp.sharepoint.com/sites/ACLS56/Shared Documents/安全性情報管理システム（パーシヴ）/ツール/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://perspectivecojp-my.sharepoint.com/personal/yoshimasa_kumano_2_perspective_co_jp/Documents/ドキュメント/GitHub/DCF2PCV/ツール/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA205414-FAF5-4FF2-8353-493D15F5334A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{FA205414-FAF5-4FF2-8353-493D15F5334A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5629CCDE-AA9B-45A1-B123-C44FBAB6B3DD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{04C7EF5D-BAF4-4773-868A-EC6F60A53FAF}"/>
   </bookViews>
@@ -33,6 +33,15 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>てｓｔ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,13 +569,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21EDFD0D-E1B9-4570-B20F-BD4A943A4AD7}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="0.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1" spans="2:2" ht="3" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -575,6 +589,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="da164a70-ebbe-4c8b-a398-a4d49ed3e9f6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9dec3b7c-98de-4a98-b901-fc41dd7296cb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101002D4DEFA805CD57449B28C6A41DC203C4" ma:contentTypeVersion="14" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="8ea4de63162ea995c32e3a59603a38b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="da164a70-ebbe-4c8b-a398-a4d49ed3e9f6" xmlns:ns3="9dec3b7c-98de-4a98-b901-fc41dd7296cb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5d3deb460addefd65cc0690573d0803" ns2:_="" ns3:_="">
     <xsd:import namespace="da164a70-ebbe-4c8b-a398-a4d49ed3e9f6"/>
@@ -803,34 +837,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="da164a70-ebbe-4c8b-a398-a4d49ed3e9f6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9dec3b7c-98de-4a98-b901-fc41dd7296cb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8C9ECE4-5201-4124-BE68-7222FBB444E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{169CA0E0-A9DC-48FC-B6B0-C1A1EF3EA5C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="da164a70-ebbe-4c8b-a398-a4d49ed3e9f6"/>
+    <ds:schemaRef ds:uri="9dec3b7c-98de-4a98-b901-fc41dd7296cb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{928BB45A-C834-4F1A-978B-1367CA8C4695}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{928BB45A-C834-4F1A-978B-1367CA8C4695}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{169CA0E0-A9DC-48FC-B6B0-C1A1EF3EA5C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8C9ECE4-5201-4124-BE68-7222FBB444E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="da164a70-ebbe-4c8b-a398-a4d49ed3e9f6"/>
+    <ds:schemaRef ds:uri="9dec3b7c-98de-4a98-b901-fc41dd7296cb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>